--- a/output/pdf_financials_xlsx/RKR.xlsx
+++ b/output/pdf_financials_xlsx/RKR.xlsx
@@ -5732,49 +5732,49 @@
         <v>0</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.27135</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.665088</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.240366</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.269092</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.233203</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.433556</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>3.003228</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>3.117641</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>3.16153</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>10.433287</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>11.143458</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>13.283373</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>13.525927</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>13.525927</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>13.822344</v>
       </c>
     </row>
     <row r="93">
@@ -6299,49 +6299,49 @@
         </is>
       </c>
       <c r="C103" s="3" t="n">
-        <v>0</v>
+        <v>-0.03776</v>
       </c>
       <c r="D103" s="3" t="n">
-        <v>0</v>
+        <v>-0.046558</v>
       </c>
       <c r="E103" s="3" t="n">
-        <v>0</v>
+        <v>0.041619</v>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0</v>
+        <v>-0.029451</v>
       </c>
       <c r="G103" s="3" t="n">
-        <v>0</v>
+        <v>0.041667</v>
       </c>
       <c r="H103" s="3" t="n">
-        <v>0</v>
+        <v>-0.001553</v>
       </c>
       <c r="I103" s="3" t="n">
-        <v>0</v>
+        <v>-0.008491</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0</v>
+        <v>0.006112</v>
       </c>
       <c r="K103" s="3" t="n">
-        <v>0</v>
+        <v>0.003462</v>
       </c>
       <c r="L103" s="3" t="n">
-        <v>0</v>
+        <v>-0.262752</v>
       </c>
       <c r="M103" s="3" t="n">
-        <v>0</v>
+        <v>0.051951</v>
       </c>
       <c r="N103" s="3" t="n">
-        <v>0</v>
+        <v>0.054537</v>
       </c>
       <c r="O103" s="3" t="n">
-        <v>0</v>
+        <v>0.14014</v>
       </c>
       <c r="P103" s="3" t="n">
-        <v>0</v>
+        <v>0.010645</v>
       </c>
       <c r="Q103" s="3" t="n">
-        <v>0</v>
+        <v>0.000291</v>
       </c>
     </row>
     <row r="104">
@@ -6470,49 +6470,49 @@
         </is>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.024382</v>
+        <v>-0.013378</v>
       </c>
       <c r="D106" s="3" t="n">
-        <v>0.070689</v>
+        <v>0.024131</v>
       </c>
       <c r="E106" s="3" t="n">
-        <v>0.40959</v>
+        <v>0.451209</v>
       </c>
       <c r="F106" s="3" t="n">
-        <v>0.402082</v>
+        <v>0.372631</v>
       </c>
       <c r="G106" s="3" t="n">
-        <v>0.21144</v>
+        <v>0.253107</v>
       </c>
       <c r="H106" s="3" t="n">
-        <v>0.11629</v>
+        <v>0.114737</v>
       </c>
       <c r="I106" s="3" t="n">
-        <v>0.123932</v>
+        <v>0.115441</v>
       </c>
       <c r="J106" s="3" t="n">
-        <v>0.144278</v>
+        <v>0.15039</v>
       </c>
       <c r="K106" s="3" t="n">
-        <v>0.218116</v>
+        <v>0.221578</v>
       </c>
       <c r="L106" s="3" t="n">
-        <v>-0.113387</v>
+        <v>-0.376139</v>
       </c>
       <c r="M106" s="3" t="n">
-        <v>-0.06135</v>
+        <v>-0.009398999999999999</v>
       </c>
       <c r="N106" s="3" t="n">
-        <v>0.164099</v>
+        <v>0.218636</v>
       </c>
       <c r="O106" s="3" t="n">
-        <v>0.813565</v>
+        <v>0.953705</v>
       </c>
       <c r="P106" s="3" t="n">
-        <v>0.354403</v>
+        <v>0.365048</v>
       </c>
       <c r="Q106" s="3" t="n">
-        <v>0.059045</v>
+        <v>0.059336</v>
       </c>
     </row>
     <row r="107">
@@ -8490,7 +8490,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -9296,7 +9300,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr">
         <is>
           <t>-</t>
@@ -10418,7 +10426,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -11064,7 +11076,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -11602,7 +11618,11 @@
           <t>Share-based payments reserve</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
@@ -14094,7 +14114,11 @@
           <t>Prepaids and deposits 5,068</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -15078,7 +15102,11 @@
           <t>Share-based payments reserve 2,233,203</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -16142,7 +16170,11 @@
           <t>Prepaids and deposits 46,735</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -17718,7 +17750,11 @@
           <t>Prepaids and deposits 17,284</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -18706,7 +18742,11 @@
           <t>Share-based payments reserve 1,269,092</t>
         </is>
       </c>
-      <c r="D111" t="inlineStr"/>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
           <t>-</t>
@@ -19774,7 +19814,11 @@
           <t>Prepaids and deposits 58,903</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr"/>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E122" t="inlineStr">
         <is>
           <t>-</t>
@@ -20458,7 +20502,11 @@
           <t>Share-based payments reserve 1,240,366</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr"/>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E129" t="inlineStr">
         <is>
           <t>-</t>
@@ -22170,7 +22218,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/RKR.xlsx
+++ b/output/pdf_financials_xlsx/RKR.xlsx
@@ -1043,10 +1043,10 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.007647</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.001745</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
@@ -2016,10 +2016,10 @@
         <v>-0.5289779999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.443226</v>
+        <v>-1.450873</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-1.971449</v>
+        <v>-1.973194</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-2.867787</v>
@@ -2130,10 +2130,10 @@
         <v>-0.5289779999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.442038</v>
+        <v>-1.449685</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-1.969667</v>
+        <v>-1.971412</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-2.856889</v>
@@ -2417,52 +2417,52 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.436645</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.09593599999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.121724</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.011436</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.010697</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.345977</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.052424</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.034837</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.020875</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>10.177283</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>4.656633</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.03318</v>
       </c>
       <c r="O34" s="3" t="n">
-        <v>0</v>
+        <v>0.025759</v>
       </c>
       <c r="P34" s="3" t="n">
-        <v>0</v>
+        <v>0.006821</v>
       </c>
       <c r="Q34" s="3" t="n">
-        <v>0</v>
+        <v>0.871023</v>
       </c>
     </row>
     <row r="35">
@@ -2527,52 +2527,52 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.436645</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>1.1</v>
+        <v>1.195936</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.9</v>
+        <v>1.021724</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.011436</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.27</v>
+        <v>0.280697</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.06</v>
+        <v>0.405977</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.049875</v>
+        <v>0.102299</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.0285</v>
+        <v>0.063337</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.020875</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>10.177283</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>4.656633</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0</v>
+        <v>0.03318</v>
       </c>
       <c r="O36" s="3" t="n">
-        <v>0</v>
+        <v>0.025759</v>
       </c>
       <c r="P36" s="3" t="n">
-        <v>0</v>
+        <v>0.006821</v>
       </c>
       <c r="Q36" s="3" t="n">
-        <v>0</v>
+        <v>0.871023</v>
       </c>
     </row>
     <row r="37">
@@ -3187,52 +3187,52 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>1e-06</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.474405</v>
+        <v>0.03776</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.108281</v>
+        <v>0.012345</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.180627</v>
+        <v>0.058903</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.02872</v>
+        <v>0.017284</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.015765</v>
+        <v>0.005068</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.352598</v>
+        <v>0.006621</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.067536</v>
+        <v>0.015112</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.043837</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.026413</v>
+        <v>0.005538</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>10.445573</v>
+        <v>0.26829</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>4.872972</v>
+        <v>0.216339</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.194982</v>
+        <v>0.161802</v>
       </c>
       <c r="O48" s="3" t="n">
-        <v>0.047421</v>
+        <v>0.021662</v>
       </c>
       <c r="P48" s="3" t="n">
-        <v>0.017838</v>
+        <v>0.011017</v>
       </c>
       <c r="Q48" s="3" t="n">
-        <v>0.881749</v>
+        <v>0.010726</v>
       </c>
     </row>
     <row r="49">
@@ -8338,7 +8338,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -13814,7 +13814,7 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -15972,7 +15972,7 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -17452,7 +17452,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -19516,7 +19516,7 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -55326,7 +55326,7 @@
       </c>
       <c r="D496" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E496" t="inlineStr">
@@ -56252,7 +56252,7 @@
       </c>
       <c r="D506" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E506" t="inlineStr">
@@ -57094,7 +57094,7 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
@@ -58498,7 +58498,7 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
@@ -60382,7 +60382,7 @@
       </c>
       <c r="D550" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E550" t="inlineStr">
@@ -62232,7 +62232,7 @@
       </c>
       <c r="D569" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E569" t="inlineStr">
@@ -63390,7 +63390,7 @@
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">

--- a/output/pdf_financials_xlsx/RKR.xlsx
+++ b/output/pdf_financials_xlsx/RKR.xlsx
@@ -755,16 +755,16 @@
         </is>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.01301</v>
+        <v>0.026423</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.07291400000000001</v>
+        <v>0.224569</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.118533</v>
+        <v>0.388771</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.119221</v>
+        <v>0.468996</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>0.272052</v>
@@ -926,16 +926,16 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.02801</v>
+        <v>0.041423</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.137998</v>
+        <v>0.289653</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.186806</v>
+        <v>0.457044</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.119221</v>
+        <v>0.468996</v>
       </c>
       <c r="G10" s="3" t="n">
         <v>0.272052</v>
@@ -4267,49 +4267,49 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.029</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.048741</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.061857</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.043155</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.055259</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.085191</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.046704</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.132705</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.097844</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.127442</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.115415</v>
       </c>
       <c r="N67" s="3" t="n">
-        <v>0</v>
+        <v>0.095415</v>
       </c>
       <c r="O67" s="3" t="n">
-        <v>0</v>
+        <v>0.146995</v>
       </c>
       <c r="P67" s="3" t="n">
-        <v>0</v>
+        <v>0.193915</v>
       </c>
       <c r="Q67" s="3" t="n">
-        <v>0</v>
+        <v>0.385415</v>
       </c>
     </row>
     <row r="68">
@@ -6758,7 +6758,7 @@
         <v>0</v>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.005345</v>
       </c>
       <c r="E111" s="3" t="n">
         <v>0</v>
@@ -7007,7 +7007,7 @@
         <v>0</v>
       </c>
       <c r="K115" s="3" t="n">
-        <v>0</v>
+        <v>0.023955</v>
       </c>
       <c r="L115" s="3" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.005345</v>
       </c>
       <c r="E134" s="3" t="n">
         <v>0</v>
@@ -8156,7 +8156,7 @@
         <v>-0.271006</v>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-1.235088</v>
+        <v>-1.240433</v>
       </c>
       <c r="E135" s="3" t="n">
         <v>-1.475156</v>
@@ -23984,7 +23984,11 @@
           <t>Shares issued for cash 34,100,000 879,450 284,550</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E166" t="inlineStr">
         <is>
           <t>-</t>
@@ -33408,7 +33412,11 @@
           <t>Proceeds from sale of marketable securities</t>
         </is>
       </c>
-      <c r="D266" t="inlineStr"/>
+      <c r="D266" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E266" t="inlineStr">
         <is>
           <t>-</t>
@@ -35224,7 +35232,11 @@
           <t>Deferred income tax recovery</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -35420,7 +35432,11 @@
           <t>Proceeds from share issuance</t>
         </is>
       </c>
-      <c r="D287" t="inlineStr"/>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E287" t="inlineStr">
         <is>
           <t>-</t>
@@ -43800,7 +43816,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D375" t="inlineStr"/>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E375" t="inlineStr">
         <is>
           <t>-</t>
@@ -46712,7 +46732,11 @@
           <t>Acquisition of equipment -</t>
         </is>
       </c>
-      <c r="D405" t="inlineStr"/>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E405" t="inlineStr">
         <is>
           <t>-</t>
@@ -47004,7 +47028,11 @@
           <t>Shares issued for cash 1,530,000</t>
         </is>
       </c>
-      <c r="D408" t="inlineStr"/>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E408" t="inlineStr">
         <is>
           <t>-</t>
@@ -50106,7 +50134,11 @@
           <t>Acquisition of equipment</t>
         </is>
       </c>
-      <c r="D440" t="inlineStr"/>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E440" t="inlineStr">
         <is>
           <t>-</t>
@@ -59336,7 +59368,11 @@
           <t>Consulting and directors’ fees (Note 12) $</t>
         </is>
       </c>
-      <c r="D539" t="inlineStr"/>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E539" t="inlineStr">
         <is>
           <t>-</t>
@@ -59810,7 +59846,11 @@
           <t>Consulting and directors’ fees (Note 11) $</t>
         </is>
       </c>
-      <c r="D544" t="inlineStr"/>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E544" t="inlineStr">
         <is>
           <t>-</t>
@@ -61052,7 +61092,11 @@
           <t>Consulting and directors’ fees (Note 12) $ 151,655 $</t>
         </is>
       </c>
-      <c r="D557" t="inlineStr"/>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E557" t="inlineStr">
         <is>
           <t>-</t>
@@ -63106,7 +63150,11 @@
           <t>Consulting and directors’ fees (Note 13)</t>
         </is>
       </c>
-      <c r="D578" t="inlineStr"/>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E578" t="inlineStr">
         <is>
           <t>-</t>
